--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3867"/>
+  <dimension ref="A1:F3868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77764,7 +77764,27 @@
         <v>56.9900016784668</v>
       </c>
       <c r="F3867" t="n">
-        <v>7073100</v>
+        <v>7107500</v>
+      </c>
+    </row>
+    <row r="3868">
+      <c r="A3868" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B3868" t="n">
+        <v>56.17</v>
+      </c>
+      <c r="C3868" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="D3868" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="E3868" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="F3868" t="n">
+        <v>704900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -77772,10 +77772,10 @@
         <v>46231</v>
       </c>
       <c r="B3868" t="n">
-        <v>56.17</v>
+        <v>56.67</v>
       </c>
       <c r="C3868" t="n">
-        <v>56.24</v>
+        <v>57.06</v>
       </c>
       <c r="D3868" t="n">
         <v>55.28</v>
@@ -77784,7 +77784,7 @@
         <v>55.4</v>
       </c>
       <c r="F3868" t="n">
-        <v>704900</v>
+        <v>5871000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -77772,7 +77772,7 @@
         <v>46231</v>
       </c>
       <c r="B3868" t="n">
-        <v>56.67</v>
+        <v>56.77</v>
       </c>
       <c r="C3868" t="n">
         <v>57.06</v>
@@ -77784,7 +77784,7 @@
         <v>55.4</v>
       </c>
       <c r="F3868" t="n">
-        <v>5871000</v>
+        <v>8452000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -77772,16 +77772,16 @@
         <v>46231</v>
       </c>
       <c r="B3868" t="n">
-        <v>56.77</v>
+        <v>56.77000045776367</v>
       </c>
       <c r="C3868" t="n">
-        <v>57.06</v>
+        <v>57.06000137329102</v>
       </c>
       <c r="D3868" t="n">
-        <v>55.28</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="E3868" t="n">
-        <v>55.4</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="F3868" t="n">
         <v>8452000</v>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3868"/>
+  <dimension ref="A1:F3869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77787,6 +77787,26 @@
         <v>8452000</v>
       </c>
     </row>
+    <row r="3869">
+      <c r="A3869" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B3869" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="C3869" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="D3869" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="E3869" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F3869" t="n">
+        <v>7720400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -77792,7 +77792,7 @@
         <v>46232</v>
       </c>
       <c r="B3869" t="n">
-        <v>58.97</v>
+        <v>58.41</v>
       </c>
       <c r="C3869" t="n">
         <v>59.08</v>
@@ -77804,7 +77804,7 @@
         <v>57.9</v>
       </c>
       <c r="F3869" t="n">
-        <v>7720400</v>
+        <v>9659100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3869"/>
+  <dimension ref="A1:F3870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77792,19 +77792,39 @@
         <v>46232</v>
       </c>
       <c r="B3869" t="n">
-        <v>58.41</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="C3869" t="n">
-        <v>59.08</v>
+        <v>59.08000183105469</v>
       </c>
       <c r="D3869" t="n">
-        <v>57.9</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="E3869" t="n">
-        <v>57.9</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="F3869" t="n">
         <v>9659100</v>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B3870" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="C3870" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="D3870" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="E3870" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="F3870" t="n">
+        <v>4338200</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3870"/>
+  <dimension ref="A1:F3871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77812,19 +77812,39 @@
         <v>46233</v>
       </c>
       <c r="B3870" t="n">
-        <v>59.96</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="C3870" t="n">
-        <v>59.97</v>
+        <v>59.97000122070312</v>
       </c>
       <c r="D3870" t="n">
-        <v>57.91</v>
+        <v>57.90999984741211</v>
       </c>
       <c r="E3870" t="n">
-        <v>58.05</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="F3870" t="n">
         <v>4338200</v>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B3871" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="C3871" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="D3871" t="n">
+        <v>59.82</v>
+      </c>
+      <c r="E3871" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="F3871" t="n">
+        <v>7174700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3871"/>
+  <dimension ref="A1:F3872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77832,19 +77832,39 @@
         <v>46234</v>
       </c>
       <c r="B3871" t="n">
-        <v>60.85</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="C3871" t="n">
-        <v>61.08</v>
+        <v>61.08000183105469</v>
       </c>
       <c r="D3871" t="n">
-        <v>59.82</v>
+        <v>59.81999969482422</v>
       </c>
       <c r="E3871" t="n">
-        <v>59.96</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="F3871" t="n">
-        <v>7174700</v>
+        <v>7178400</v>
+      </c>
+    </row>
+    <row r="3872">
+      <c r="A3872" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B3872" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C3872" t="n">
+        <v>59.55</v>
+      </c>
+      <c r="D3872" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="E3872" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="F3872" t="n">
+        <v>7072400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -77829,42 +77829,42 @@
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B3871" t="n">
-        <v>60.84999847412109</v>
+        <v>58.5</v>
       </c>
       <c r="C3871" t="n">
-        <v>61.08000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3871" t="n">
-        <v>59.81999969482422</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3871" t="n">
-        <v>59.95999908447266</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3871" t="n">
-        <v>7178400</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.5</v>
+        <v>58.45</v>
       </c>
       <c r="C3872" t="n">
-        <v>59.55</v>
+        <v>58.58</v>
       </c>
       <c r="D3872" t="n">
-        <v>58.44</v>
+        <v>56.95</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.65</v>
+        <v>58.2</v>
       </c>
       <c r="F3872" t="n">
-        <v>7072400</v>
+        <v>8390100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3872"/>
+  <dimension ref="A1:F3874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77829,42 +77829,82 @@
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.5</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="C3871" t="n">
-        <v>59.54999923706055</v>
+        <v>61.08000183105469</v>
       </c>
       <c r="D3871" t="n">
-        <v>58.43999862670898</v>
+        <v>59.81999969482422</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.65000152587891</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="F3871" t="n">
-        <v>7072400</v>
+        <v>7178400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B3872" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="C3872" t="n">
+        <v>59.54999923706055</v>
+      </c>
+      <c r="D3872" t="n">
+        <v>58.43999862670898</v>
+      </c>
+      <c r="E3872" t="n">
+        <v>58.65000152587891</v>
+      </c>
+      <c r="F3872" t="n">
+        <v>7072400</v>
+      </c>
+    </row>
+    <row r="3873">
+      <c r="A3873" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="B3872" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="C3872" t="n">
-        <v>58.58</v>
-      </c>
-      <c r="D3872" t="n">
-        <v>56.95</v>
-      </c>
-      <c r="E3872" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="F3872" t="n">
+      <c r="B3873" t="n">
+        <v>58.45000076293945</v>
+      </c>
+      <c r="C3873" t="n">
+        <v>58.58000183105469</v>
+      </c>
+      <c r="D3873" t="n">
+        <v>56.95000076293945</v>
+      </c>
+      <c r="E3873" t="n">
+        <v>58.20000076293945</v>
+      </c>
+      <c r="F3873" t="n">
         <v>8390100</v>
+      </c>
+    </row>
+    <row r="3874">
+      <c r="A3874" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B3874" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="C3874" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="D3874" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="E3874" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="F3874" t="n">
+        <v>9994900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3874"/>
+  <dimension ref="A1:F3875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77892,19 +77892,39 @@
         <v>46239</v>
       </c>
       <c r="B3874" t="n">
-        <v>59.2</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.99</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.21</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.21</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3874" t="n">
         <v>9994900</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B3875" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="C3875" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="D3875" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="E3875" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F3875" t="n">
+        <v>8406900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3875"/>
+  <dimension ref="A1:F3874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77829,101 +77829,81 @@
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B3871" t="n">
-        <v>60.84999847412109</v>
+        <v>58.5</v>
       </c>
       <c r="C3871" t="n">
-        <v>61.08000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3871" t="n">
-        <v>59.81999969482422</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3871" t="n">
-        <v>59.95999908447266</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3871" t="n">
-        <v>7178400</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.5</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3872" t="n">
-        <v>59.54999923706055</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3872" t="n">
-        <v>58.43999862670898</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.65000152587891</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3872" t="n">
-        <v>7072400</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B3873" t="n">
-        <v>58.45000076293945</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3873" t="n">
-        <v>58.58000183105469</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3873" t="n">
-        <v>56.95000076293945</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3873" t="n">
-        <v>58.20000076293945</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3873" t="n">
-        <v>8390100</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B3874" t="n">
-        <v>59.20000076293945</v>
+        <v>58.61</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.9900016784668</v>
+        <v>59.78</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.20999908447266</v>
+        <v>58.46</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.20999908447266</v>
+        <v>59.5</v>
       </c>
       <c r="F3874" t="n">
-        <v>9994900</v>
-      </c>
-    </row>
-    <row r="3875">
-      <c r="A3875" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="B3875" t="n">
-        <v>58.61</v>
-      </c>
-      <c r="C3875" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="D3875" t="n">
-        <v>58.46</v>
-      </c>
-      <c r="E3875" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="F3875" t="n">
         <v>8406900</v>
       </c>
     </row>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3874"/>
+  <dimension ref="A1:F3875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77892,19 +77892,39 @@
         <v>46240</v>
       </c>
       <c r="B3874" t="n">
-        <v>58.61</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.78</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.46</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3874" t="n">
         <v>59.5</v>
       </c>
       <c r="F3874" t="n">
         <v>8406900</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B3875" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="C3875" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="D3875" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="E3875" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="F3875" t="n">
+        <v>5821000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3875"/>
+  <dimension ref="A1:F3877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77829,102 +77829,142 @@
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.5</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="C3871" t="n">
-        <v>59.54999923706055</v>
+        <v>61.08000183105469</v>
       </c>
       <c r="D3871" t="n">
-        <v>58.43999862670898</v>
+        <v>59.81999969482422</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.65000152587891</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="F3871" t="n">
-        <v>7072400</v>
+        <v>7178400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.45000076293945</v>
+        <v>58.5</v>
       </c>
       <c r="C3872" t="n">
-        <v>58.58000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3872" t="n">
-        <v>56.95000076293945</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.20000076293945</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3872" t="n">
-        <v>8390100</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B3873" t="n">
-        <v>59.20000076293945</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3873" t="n">
-        <v>59.9900016784668</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3873" t="n">
-        <v>58.20999908447266</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3873" t="n">
-        <v>59.20999908447266</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3873" t="n">
-        <v>9994900</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B3874" t="n">
-        <v>58.61000061035156</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.77999877929688</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.45999908447266</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.5</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3874" t="n">
-        <v>8406900</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B3875" t="n">
+        <v>58.61000061035156</v>
+      </c>
+      <c r="C3875" t="n">
+        <v>59.77999877929688</v>
+      </c>
+      <c r="D3875" t="n">
+        <v>58.45999908447266</v>
+      </c>
+      <c r="E3875" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F3875" t="n">
+        <v>8406900</v>
+      </c>
+    </row>
+    <row r="3876">
+      <c r="A3876" s="1" t="n">
         <v>46241</v>
       </c>
-      <c r="B3875" t="n">
-        <v>57.45</v>
-      </c>
-      <c r="C3875" t="n">
-        <v>58.93</v>
-      </c>
-      <c r="D3875" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="E3875" t="n">
+      <c r="B3876" t="n">
+        <v>57.45000076293945</v>
+      </c>
+      <c r="C3876" t="n">
+        <v>58.93000030517578</v>
+      </c>
+      <c r="D3876" t="n">
+        <v>57.34999847412109</v>
+      </c>
+      <c r="E3876" t="n">
         <v>58.5</v>
       </c>
-      <c r="F3875" t="n">
+      <c r="F3876" t="n">
         <v>5821000</v>
+      </c>
+    </row>
+    <row r="3877">
+      <c r="A3877" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B3877" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="C3877" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="D3877" t="n">
+        <v>58.32</v>
+      </c>
+      <c r="E3877" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="F3877" t="n">
+        <v>9826700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3877"/>
+  <dimension ref="A1:F3878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77952,19 +77952,39 @@
         <v>46244</v>
       </c>
       <c r="B3877" t="n">
-        <v>61.24</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="C3877" t="n">
-        <v>61.24</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.32</v>
+        <v>58.31999969482422</v>
       </c>
       <c r="E3877" t="n">
-        <v>58.35</v>
+        <v>58.34999847412109</v>
       </c>
       <c r="F3877" t="n">
         <v>9826700</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B3878" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="C3878" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="D3878" t="n">
+        <v>58.85</v>
+      </c>
+      <c r="E3878" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="F3878" t="n">
+        <v>7752700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3878"/>
+  <dimension ref="A1:F3877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77829,162 +77829,142 @@
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B3871" t="n">
-        <v>60.84999847412109</v>
+        <v>58.5</v>
       </c>
       <c r="C3871" t="n">
-        <v>61.08000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3871" t="n">
-        <v>59.81999969482422</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3871" t="n">
-        <v>59.95999908447266</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3871" t="n">
-        <v>7178400</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.5</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3872" t="n">
-        <v>59.54999923706055</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3872" t="n">
-        <v>58.43999862670898</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.65000152587891</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3872" t="n">
-        <v>7072400</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B3873" t="n">
-        <v>58.45000076293945</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3873" t="n">
-        <v>58.58000183105469</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3873" t="n">
-        <v>56.95000076293945</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3873" t="n">
-        <v>58.20000076293945</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3873" t="n">
-        <v>8390100</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B3874" t="n">
-        <v>59.20000076293945</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.9900016784668</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.20999908447266</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.20999908447266</v>
+        <v>59.5</v>
       </c>
       <c r="F3874" t="n">
-        <v>9994900</v>
+        <v>8406900</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B3875" t="n">
-        <v>58.61000061035156</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="C3875" t="n">
-        <v>59.77999877929688</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3875" t="n">
-        <v>58.45999908447266</v>
+        <v>57.34999847412109</v>
       </c>
       <c r="E3875" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="F3875" t="n">
-        <v>8406900</v>
+        <v>5821000</v>
       </c>
     </row>
     <row r="3876">
       <c r="A3876" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B3876" t="n">
-        <v>57.45000076293945</v>
+        <v>59.25</v>
       </c>
       <c r="C3876" t="n">
-        <v>58.93000030517578</v>
+        <v>61.72999954223633</v>
       </c>
       <c r="D3876" t="n">
-        <v>57.34999847412109</v>
+        <v>58.84999847412109</v>
       </c>
       <c r="E3876" t="n">
-        <v>58.5</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="F3876" t="n">
-        <v>5821000</v>
+        <v>7752700</v>
       </c>
     </row>
     <row r="3877">
       <c r="A3877" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B3877" t="n">
-        <v>61.2400016784668</v>
+        <v>59.14</v>
       </c>
       <c r="C3877" t="n">
-        <v>61.2400016784668</v>
+        <v>59.81</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.31999969482422</v>
+        <v>58.74</v>
       </c>
       <c r="E3877" t="n">
-        <v>58.34999847412109</v>
+        <v>59.19</v>
       </c>
       <c r="F3877" t="n">
-        <v>9826700</v>
-      </c>
-    </row>
-    <row r="3878">
-      <c r="A3878" s="1" t="n">
-        <v>46245</v>
-      </c>
-      <c r="B3878" t="n">
-        <v>59.25</v>
-      </c>
-      <c r="C3878" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="D3878" t="n">
-        <v>58.85</v>
-      </c>
-      <c r="E3878" t="n">
-        <v>61.36</v>
-      </c>
-      <c r="F3878" t="n">
-        <v>7752700</v>
+        <v>5522800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3877"/>
+  <dimension ref="A1:F3878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77952,19 +77952,39 @@
         <v>46246</v>
       </c>
       <c r="B3877" t="n">
-        <v>59.14</v>
+        <v>59.13999938964844</v>
       </c>
       <c r="C3877" t="n">
-        <v>59.81</v>
+        <v>59.81000137329102</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.74</v>
+        <v>58.7400016784668</v>
       </c>
       <c r="E3877" t="n">
-        <v>59.19</v>
+        <v>59.18999862670898</v>
       </c>
       <c r="F3877" t="n">
         <v>5522800</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B3878" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="C3878" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="D3878" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="E3878" t="n">
+        <v>58.49</v>
+      </c>
+      <c r="F3878" t="n">
+        <v>4500100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3878"/>
+  <dimension ref="A1:F3879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77649,282 +77649,282 @@
     </row>
     <row r="3862">
       <c r="A3862" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B3862" t="n">
-        <v>57.68999862670898</v>
+        <v>58.18000030517578</v>
       </c>
       <c r="C3862" t="n">
-        <v>58.72000122070312</v>
+        <v>58.95999908447266</v>
       </c>
       <c r="D3862" t="n">
-        <v>57.61999893188477</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="E3862" t="n">
-        <v>57.84999847412109</v>
+        <v>58.15000152587891</v>
       </c>
       <c r="F3862" t="n">
-        <v>4940000</v>
+        <v>4489200</v>
       </c>
     </row>
     <row r="3863">
       <c r="A3863" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B3863" t="n">
-        <v>58.18000030517578</v>
+        <v>59.77000045776367</v>
       </c>
       <c r="C3863" t="n">
-        <v>58.95999908447266</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3863" t="n">
-        <v>58.11000061035156</v>
+        <v>58.65999984741211</v>
       </c>
       <c r="E3863" t="n">
-        <v>58.15000152587891</v>
+        <v>58.90999984741211</v>
       </c>
       <c r="F3863" t="n">
-        <v>4489200</v>
+        <v>5041800</v>
       </c>
     </row>
     <row r="3864">
       <c r="A3864" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B3864" t="n">
-        <v>59.77000045776367</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="C3864" t="n">
-        <v>59.9900016784668</v>
+        <v>61.34999847412109</v>
       </c>
       <c r="D3864" t="n">
-        <v>58.65999984741211</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="E3864" t="n">
-        <v>58.90999984741211</v>
+        <v>61</v>
       </c>
       <c r="F3864" t="n">
-        <v>5041800</v>
+        <v>6359200</v>
       </c>
     </row>
     <row r="3865">
       <c r="A3865" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B3865" t="n">
-        <v>60.54000091552734</v>
+        <v>58.81999969482422</v>
       </c>
       <c r="C3865" t="n">
-        <v>61.34999847412109</v>
+        <v>60.27000045776367</v>
       </c>
       <c r="D3865" t="n">
-        <v>60.54000091552734</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3865" t="n">
-        <v>61</v>
+        <v>59.83000183105469</v>
       </c>
       <c r="F3865" t="n">
-        <v>6359200</v>
+        <v>5376700</v>
       </c>
     </row>
     <row r="3866">
       <c r="A3866" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B3866" t="n">
-        <v>58.81999969482422</v>
+        <v>55.70999908447266</v>
       </c>
       <c r="C3866" t="n">
-        <v>60.27000045776367</v>
+        <v>57.5</v>
       </c>
       <c r="D3866" t="n">
-        <v>58.45999908447266</v>
+        <v>55.70000076293945</v>
       </c>
       <c r="E3866" t="n">
-        <v>59.83000183105469</v>
+        <v>56.9900016784668</v>
       </c>
       <c r="F3866" t="n">
-        <v>5376700</v>
+        <v>7107500</v>
       </c>
     </row>
     <row r="3867">
       <c r="A3867" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B3867" t="n">
-        <v>55.70999908447266</v>
+        <v>56.77000045776367</v>
       </c>
       <c r="C3867" t="n">
-        <v>57.5</v>
+        <v>57.06000137329102</v>
       </c>
       <c r="D3867" t="n">
-        <v>55.70000076293945</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="E3867" t="n">
-        <v>56.9900016784668</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="F3867" t="n">
-        <v>7107500</v>
+        <v>8452000</v>
       </c>
     </row>
     <row r="3868">
       <c r="A3868" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B3868" t="n">
-        <v>56.77000045776367</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="C3868" t="n">
-        <v>57.06000137329102</v>
+        <v>59.08000183105469</v>
       </c>
       <c r="D3868" t="n">
-        <v>55.27999877929688</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="E3868" t="n">
-        <v>55.40000152587891</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="F3868" t="n">
-        <v>8452000</v>
+        <v>9659100</v>
       </c>
     </row>
     <row r="3869">
       <c r="A3869" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B3869" t="n">
-        <v>58.40999984741211</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="C3869" t="n">
-        <v>59.08000183105469</v>
+        <v>59.97000122070312</v>
       </c>
       <c r="D3869" t="n">
-        <v>57.90000152587891</v>
+        <v>57.90999984741211</v>
       </c>
       <c r="E3869" t="n">
-        <v>57.90000152587891</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="F3869" t="n">
-        <v>9659100</v>
+        <v>4338200</v>
       </c>
     </row>
     <row r="3870">
       <c r="A3870" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B3870" t="n">
-        <v>59.95999908447266</v>
+        <v>58.5</v>
       </c>
       <c r="C3870" t="n">
-        <v>59.97000122070312</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3870" t="n">
-        <v>57.90999984741211</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3870" t="n">
-        <v>58.04999923706055</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3870" t="n">
-        <v>4338200</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.5</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3871" t="n">
-        <v>59.54999923706055</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3871" t="n">
-        <v>58.43999862670898</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.65000152587891</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3871" t="n">
-        <v>7072400</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.45000076293945</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3872" t="n">
-        <v>58.58000183105469</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3872" t="n">
-        <v>56.95000076293945</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.20000076293945</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3872" t="n">
-        <v>8390100</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B3873" t="n">
-        <v>59.20000076293945</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3873" t="n">
-        <v>59.9900016784668</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3873" t="n">
-        <v>58.20999908447266</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3873" t="n">
-        <v>59.20999908447266</v>
+        <v>59.5</v>
       </c>
       <c r="F3873" t="n">
-        <v>9994900</v>
+        <v>8406900</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B3874" t="n">
-        <v>58.61000061035156</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.77999877929688</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.45999908447266</v>
+        <v>57.34999847412109</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="F3874" t="n">
-        <v>8406900</v>
+        <v>5821000</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B3875" t="n">
-        <v>57.45000076293945</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="C3875" t="n">
-        <v>58.93000030517578</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="D3875" t="n">
-        <v>57.34999847412109</v>
+        <v>58.31999969482422</v>
       </c>
       <c r="E3875" t="n">
-        <v>58.5</v>
+        <v>58.34999847412109</v>
       </c>
       <c r="F3875" t="n">
-        <v>5821000</v>
+        <v>9826700</v>
       </c>
     </row>
     <row r="3876">
@@ -77972,19 +77972,39 @@
         <v>46247</v>
       </c>
       <c r="B3878" t="n">
-        <v>59.07</v>
+        <v>59.06999969482422</v>
       </c>
       <c r="C3878" t="n">
-        <v>59.69</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D3878" t="n">
-        <v>57.93</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="E3878" t="n">
-        <v>58.49</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="F3878" t="n">
         <v>4500100</v>
+      </c>
+    </row>
+    <row r="3879">
+      <c r="A3879" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B3879" t="n">
+        <v>58.63</v>
+      </c>
+      <c r="C3879" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="D3879" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="E3879" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="F3879" t="n">
+        <v>4985900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3879"/>
+  <dimension ref="A1:F3880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77649,282 +77649,282 @@
     </row>
     <row r="3862">
       <c r="A3862" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B3862" t="n">
-        <v>58.18000030517578</v>
+        <v>57.68999862670898</v>
       </c>
       <c r="C3862" t="n">
-        <v>58.95999908447266</v>
+        <v>58.72000122070312</v>
       </c>
       <c r="D3862" t="n">
-        <v>58.11000061035156</v>
+        <v>57.61999893188477</v>
       </c>
       <c r="E3862" t="n">
-        <v>58.15000152587891</v>
+        <v>57.84999847412109</v>
       </c>
       <c r="F3862" t="n">
-        <v>4489200</v>
+        <v>4940000</v>
       </c>
     </row>
     <row r="3863">
       <c r="A3863" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B3863" t="n">
-        <v>59.77000045776367</v>
+        <v>58.18000030517578</v>
       </c>
       <c r="C3863" t="n">
-        <v>59.9900016784668</v>
+        <v>58.95999908447266</v>
       </c>
       <c r="D3863" t="n">
-        <v>58.65999984741211</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="E3863" t="n">
-        <v>58.90999984741211</v>
+        <v>58.15000152587891</v>
       </c>
       <c r="F3863" t="n">
-        <v>5041800</v>
+        <v>4489200</v>
       </c>
     </row>
     <row r="3864">
       <c r="A3864" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B3864" t="n">
-        <v>60.54000091552734</v>
+        <v>59.77000045776367</v>
       </c>
       <c r="C3864" t="n">
-        <v>61.34999847412109</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3864" t="n">
-        <v>60.54000091552734</v>
+        <v>58.65999984741211</v>
       </c>
       <c r="E3864" t="n">
-        <v>61</v>
+        <v>58.90999984741211</v>
       </c>
       <c r="F3864" t="n">
-        <v>6359200</v>
+        <v>5041800</v>
       </c>
     </row>
     <row r="3865">
       <c r="A3865" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B3865" t="n">
-        <v>58.81999969482422</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="C3865" t="n">
-        <v>60.27000045776367</v>
+        <v>61.34999847412109</v>
       </c>
       <c r="D3865" t="n">
-        <v>58.45999908447266</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="E3865" t="n">
-        <v>59.83000183105469</v>
+        <v>61</v>
       </c>
       <c r="F3865" t="n">
-        <v>5376700</v>
+        <v>6359200</v>
       </c>
     </row>
     <row r="3866">
       <c r="A3866" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B3866" t="n">
-        <v>55.70999908447266</v>
+        <v>58.81999969482422</v>
       </c>
       <c r="C3866" t="n">
-        <v>57.5</v>
+        <v>60.27000045776367</v>
       </c>
       <c r="D3866" t="n">
-        <v>55.70000076293945</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3866" t="n">
-        <v>56.9900016784668</v>
+        <v>59.83000183105469</v>
       </c>
       <c r="F3866" t="n">
-        <v>7107500</v>
+        <v>5376700</v>
       </c>
     </row>
     <row r="3867">
       <c r="A3867" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B3867" t="n">
-        <v>56.77000045776367</v>
+        <v>55.70999908447266</v>
       </c>
       <c r="C3867" t="n">
-        <v>57.06000137329102</v>
+        <v>57.5</v>
       </c>
       <c r="D3867" t="n">
-        <v>55.27999877929688</v>
+        <v>55.70000076293945</v>
       </c>
       <c r="E3867" t="n">
-        <v>55.40000152587891</v>
+        <v>56.9900016784668</v>
       </c>
       <c r="F3867" t="n">
-        <v>8452000</v>
+        <v>7107500</v>
       </c>
     </row>
     <row r="3868">
       <c r="A3868" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B3868" t="n">
-        <v>58.40999984741211</v>
+        <v>56.77000045776367</v>
       </c>
       <c r="C3868" t="n">
-        <v>59.08000183105469</v>
+        <v>57.06000137329102</v>
       </c>
       <c r="D3868" t="n">
-        <v>57.90000152587891</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="E3868" t="n">
-        <v>57.90000152587891</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="F3868" t="n">
-        <v>9659100</v>
+        <v>8452000</v>
       </c>
     </row>
     <row r="3869">
       <c r="A3869" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B3869" t="n">
-        <v>59.95999908447266</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="C3869" t="n">
-        <v>59.97000122070312</v>
+        <v>59.08000183105469</v>
       </c>
       <c r="D3869" t="n">
-        <v>57.90999984741211</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="E3869" t="n">
-        <v>58.04999923706055</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="F3869" t="n">
-        <v>4338200</v>
+        <v>9659100</v>
       </c>
     </row>
     <row r="3870">
       <c r="A3870" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B3870" t="n">
-        <v>58.5</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="C3870" t="n">
-        <v>59.54999923706055</v>
+        <v>59.97000122070312</v>
       </c>
       <c r="D3870" t="n">
-        <v>58.43999862670898</v>
+        <v>57.90999984741211</v>
       </c>
       <c r="E3870" t="n">
-        <v>58.65000152587891</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="F3870" t="n">
-        <v>7072400</v>
+        <v>4338200</v>
       </c>
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.45000076293945</v>
+        <v>58.5</v>
       </c>
       <c r="C3871" t="n">
-        <v>58.58000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3871" t="n">
-        <v>56.95000076293945</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.20000076293945</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3871" t="n">
-        <v>8390100</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B3872" t="n">
-        <v>59.20000076293945</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3872" t="n">
-        <v>59.9900016784668</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3872" t="n">
-        <v>58.20999908447266</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3872" t="n">
-        <v>59.20999908447266</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3872" t="n">
-        <v>9994900</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B3873" t="n">
-        <v>58.61000061035156</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3873" t="n">
-        <v>59.77999877929688</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3873" t="n">
-        <v>58.45999908447266</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3873" t="n">
-        <v>59.5</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3873" t="n">
-        <v>8406900</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B3874" t="n">
-        <v>57.45000076293945</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3874" t="n">
-        <v>58.93000030517578</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3874" t="n">
-        <v>57.34999847412109</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3874" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="F3874" t="n">
-        <v>5821000</v>
+        <v>8406900</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B3875" t="n">
-        <v>61.2400016784668</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="C3875" t="n">
-        <v>61.2400016784668</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3875" t="n">
-        <v>58.31999969482422</v>
+        <v>57.34999847412109</v>
       </c>
       <c r="E3875" t="n">
-        <v>58.34999847412109</v>
+        <v>58.5</v>
       </c>
       <c r="F3875" t="n">
-        <v>9826700</v>
+        <v>5821000</v>
       </c>
     </row>
     <row r="3876">
@@ -77992,19 +77992,39 @@
         <v>46248</v>
       </c>
       <c r="B3879" t="n">
-        <v>58.63</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="C3879" t="n">
-        <v>59.39</v>
+        <v>59.38999938964844</v>
       </c>
       <c r="D3879" t="n">
-        <v>58.55</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="E3879" t="n">
-        <v>58.55</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="F3879" t="n">
-        <v>4985900</v>
+        <v>4986100</v>
+      </c>
+    </row>
+    <row r="3880">
+      <c r="A3880" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B3880" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="C3880" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="D3880" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="E3880" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="F3880" t="n">
+        <v>9794400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3880"/>
+  <dimension ref="A1:F3881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78012,19 +78012,39 @@
         <v>46251</v>
       </c>
       <c r="B3880" t="n">
-        <v>61.58</v>
+        <v>61.58000183105469</v>
       </c>
       <c r="C3880" t="n">
-        <v>61.91</v>
+        <v>61.90999984741211</v>
       </c>
       <c r="D3880" t="n">
-        <v>58.71</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="E3880" t="n">
-        <v>58.71</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="F3880" t="n">
         <v>9794400</v>
+      </c>
+    </row>
+    <row r="3881">
+      <c r="A3881" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B3881" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C3881" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="D3881" t="n">
+        <v>60.97</v>
+      </c>
+      <c r="E3881" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F3881" t="n">
+        <v>5383200</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3881"/>
+  <dimension ref="A1:F3882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77649,282 +77649,282 @@
     </row>
     <row r="3862">
       <c r="A3862" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B3862" t="n">
-        <v>57.68999862670898</v>
+        <v>58.18000030517578</v>
       </c>
       <c r="C3862" t="n">
-        <v>58.72000122070312</v>
+        <v>58.95999908447266</v>
       </c>
       <c r="D3862" t="n">
-        <v>57.61999893188477</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="E3862" t="n">
-        <v>57.84999847412109</v>
+        <v>58.15000152587891</v>
       </c>
       <c r="F3862" t="n">
-        <v>4940000</v>
+        <v>4489200</v>
       </c>
     </row>
     <row r="3863">
       <c r="A3863" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B3863" t="n">
-        <v>58.18000030517578</v>
+        <v>59.77000045776367</v>
       </c>
       <c r="C3863" t="n">
-        <v>58.95999908447266</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3863" t="n">
-        <v>58.11000061035156</v>
+        <v>58.65999984741211</v>
       </c>
       <c r="E3863" t="n">
-        <v>58.15000152587891</v>
+        <v>58.90999984741211</v>
       </c>
       <c r="F3863" t="n">
-        <v>4489200</v>
+        <v>5041800</v>
       </c>
     </row>
     <row r="3864">
       <c r="A3864" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B3864" t="n">
-        <v>59.77000045776367</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="C3864" t="n">
-        <v>59.9900016784668</v>
+        <v>61.34999847412109</v>
       </c>
       <c r="D3864" t="n">
-        <v>58.65999984741211</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="E3864" t="n">
-        <v>58.90999984741211</v>
+        <v>61</v>
       </c>
       <c r="F3864" t="n">
-        <v>5041800</v>
+        <v>6359200</v>
       </c>
     </row>
     <row r="3865">
       <c r="A3865" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B3865" t="n">
-        <v>60.54000091552734</v>
+        <v>58.81999969482422</v>
       </c>
       <c r="C3865" t="n">
-        <v>61.34999847412109</v>
+        <v>60.27000045776367</v>
       </c>
       <c r="D3865" t="n">
-        <v>60.54000091552734</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3865" t="n">
-        <v>61</v>
+        <v>59.83000183105469</v>
       </c>
       <c r="F3865" t="n">
-        <v>6359200</v>
+        <v>5376700</v>
       </c>
     </row>
     <row r="3866">
       <c r="A3866" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B3866" t="n">
-        <v>58.81999969482422</v>
+        <v>55.70999908447266</v>
       </c>
       <c r="C3866" t="n">
-        <v>60.27000045776367</v>
+        <v>57.5</v>
       </c>
       <c r="D3866" t="n">
-        <v>58.45999908447266</v>
+        <v>55.70000076293945</v>
       </c>
       <c r="E3866" t="n">
-        <v>59.83000183105469</v>
+        <v>56.9900016784668</v>
       </c>
       <c r="F3866" t="n">
-        <v>5376700</v>
+        <v>7107500</v>
       </c>
     </row>
     <row r="3867">
       <c r="A3867" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B3867" t="n">
-        <v>55.70999908447266</v>
+        <v>56.77000045776367</v>
       </c>
       <c r="C3867" t="n">
-        <v>57.5</v>
+        <v>57.06000137329102</v>
       </c>
       <c r="D3867" t="n">
-        <v>55.70000076293945</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="E3867" t="n">
-        <v>56.9900016784668</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="F3867" t="n">
-        <v>7107500</v>
+        <v>8452000</v>
       </c>
     </row>
     <row r="3868">
       <c r="A3868" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B3868" t="n">
-        <v>56.77000045776367</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="C3868" t="n">
-        <v>57.06000137329102</v>
+        <v>59.08000183105469</v>
       </c>
       <c r="D3868" t="n">
-        <v>55.27999877929688</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="E3868" t="n">
-        <v>55.40000152587891</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="F3868" t="n">
-        <v>8452000</v>
+        <v>9659100</v>
       </c>
     </row>
     <row r="3869">
       <c r="A3869" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B3869" t="n">
-        <v>58.40999984741211</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="C3869" t="n">
-        <v>59.08000183105469</v>
+        <v>59.97000122070312</v>
       </c>
       <c r="D3869" t="n">
-        <v>57.90000152587891</v>
+        <v>57.90999984741211</v>
       </c>
       <c r="E3869" t="n">
-        <v>57.90000152587891</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="F3869" t="n">
-        <v>9659100</v>
+        <v>4338200</v>
       </c>
     </row>
     <row r="3870">
       <c r="A3870" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B3870" t="n">
-        <v>59.95999908447266</v>
+        <v>58.5</v>
       </c>
       <c r="C3870" t="n">
-        <v>59.97000122070312</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3870" t="n">
-        <v>57.90999984741211</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3870" t="n">
-        <v>58.04999923706055</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3870" t="n">
-        <v>4338200</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.5</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3871" t="n">
-        <v>59.54999923706055</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3871" t="n">
-        <v>58.43999862670898</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.65000152587891</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3871" t="n">
-        <v>7072400</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.45000076293945</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3872" t="n">
-        <v>58.58000183105469</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3872" t="n">
-        <v>56.95000076293945</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.20000076293945</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3872" t="n">
-        <v>8390100</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B3873" t="n">
-        <v>59.20000076293945</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3873" t="n">
-        <v>59.9900016784668</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3873" t="n">
-        <v>58.20999908447266</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3873" t="n">
-        <v>59.20999908447266</v>
+        <v>59.5</v>
       </c>
       <c r="F3873" t="n">
-        <v>9994900</v>
+        <v>8406900</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B3874" t="n">
-        <v>58.61000061035156</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.77999877929688</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.45999908447266</v>
+        <v>57.34999847412109</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="F3874" t="n">
-        <v>8406900</v>
+        <v>5821000</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B3875" t="n">
-        <v>57.45000076293945</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="C3875" t="n">
-        <v>58.93000030517578</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="D3875" t="n">
-        <v>57.34999847412109</v>
+        <v>58.31999969482422</v>
       </c>
       <c r="E3875" t="n">
-        <v>58.5</v>
+        <v>58.34999847412109</v>
       </c>
       <c r="F3875" t="n">
-        <v>5821000</v>
+        <v>9826700</v>
       </c>
     </row>
     <row r="3876">
@@ -78035,16 +78035,36 @@
         <v>61.5</v>
       </c>
       <c r="C3881" t="n">
-        <v>62.27</v>
+        <v>62.27000045776367</v>
       </c>
       <c r="D3881" t="n">
-        <v>60.97</v>
+        <v>60.97000122070312</v>
       </c>
       <c r="E3881" t="n">
-        <v>61.8</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="F3881" t="n">
         <v>5383200</v>
+      </c>
+    </row>
+    <row r="3882">
+      <c r="A3882" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B3882" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="C3882" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="D3882" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="E3882" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3882" t="n">
+        <v>6589300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3882"/>
+  <dimension ref="A1:F3883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77649,282 +77649,282 @@
     </row>
     <row r="3862">
       <c r="A3862" s="1" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B3862" t="n">
-        <v>58.18000030517578</v>
+        <v>57.68999862670898</v>
       </c>
       <c r="C3862" t="n">
-        <v>58.95999908447266</v>
+        <v>58.72000122070312</v>
       </c>
       <c r="D3862" t="n">
-        <v>58.11000061035156</v>
+        <v>57.61999893188477</v>
       </c>
       <c r="E3862" t="n">
-        <v>58.15000152587891</v>
+        <v>57.84999847412109</v>
       </c>
       <c r="F3862" t="n">
-        <v>4489200</v>
+        <v>4940000</v>
       </c>
     </row>
     <row r="3863">
       <c r="A3863" s="1" t="n">
-        <v>46225</v>
+        <v>46224</v>
       </c>
       <c r="B3863" t="n">
-        <v>59.77000045776367</v>
+        <v>58.18000030517578</v>
       </c>
       <c r="C3863" t="n">
-        <v>59.9900016784668</v>
+        <v>58.95999908447266</v>
       </c>
       <c r="D3863" t="n">
-        <v>58.65999984741211</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="E3863" t="n">
-        <v>58.90999984741211</v>
+        <v>58.15000152587891</v>
       </c>
       <c r="F3863" t="n">
-        <v>5041800</v>
+        <v>4489200</v>
       </c>
     </row>
     <row r="3864">
       <c r="A3864" s="1" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B3864" t="n">
-        <v>60.54000091552734</v>
+        <v>59.77000045776367</v>
       </c>
       <c r="C3864" t="n">
-        <v>61.34999847412109</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3864" t="n">
-        <v>60.54000091552734</v>
+        <v>58.65999984741211</v>
       </c>
       <c r="E3864" t="n">
-        <v>61</v>
+        <v>58.90999984741211</v>
       </c>
       <c r="F3864" t="n">
-        <v>6359200</v>
+        <v>5041800</v>
       </c>
     </row>
     <row r="3865">
       <c r="A3865" s="1" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B3865" t="n">
-        <v>58.81999969482422</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="C3865" t="n">
-        <v>60.27000045776367</v>
+        <v>61.34999847412109</v>
       </c>
       <c r="D3865" t="n">
-        <v>58.45999908447266</v>
+        <v>60.54000091552734</v>
       </c>
       <c r="E3865" t="n">
-        <v>59.83000183105469</v>
+        <v>61</v>
       </c>
       <c r="F3865" t="n">
-        <v>5376700</v>
+        <v>6359200</v>
       </c>
     </row>
     <row r="3866">
       <c r="A3866" s="1" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B3866" t="n">
-        <v>55.70999908447266</v>
+        <v>58.81999969482422</v>
       </c>
       <c r="C3866" t="n">
-        <v>57.5</v>
+        <v>60.27000045776367</v>
       </c>
       <c r="D3866" t="n">
-        <v>55.70000076293945</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3866" t="n">
-        <v>56.9900016784668</v>
+        <v>59.83000183105469</v>
       </c>
       <c r="F3866" t="n">
-        <v>7107500</v>
+        <v>5376700</v>
       </c>
     </row>
     <row r="3867">
       <c r="A3867" s="1" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B3867" t="n">
-        <v>56.77000045776367</v>
+        <v>55.70999908447266</v>
       </c>
       <c r="C3867" t="n">
-        <v>57.06000137329102</v>
+        <v>57.5</v>
       </c>
       <c r="D3867" t="n">
-        <v>55.27999877929688</v>
+        <v>55.70000076293945</v>
       </c>
       <c r="E3867" t="n">
-        <v>55.40000152587891</v>
+        <v>56.9900016784668</v>
       </c>
       <c r="F3867" t="n">
-        <v>8452000</v>
+        <v>7107500</v>
       </c>
     </row>
     <row r="3868">
       <c r="A3868" s="1" t="n">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="B3868" t="n">
-        <v>58.40999984741211</v>
+        <v>56.77000045776367</v>
       </c>
       <c r="C3868" t="n">
-        <v>59.08000183105469</v>
+        <v>57.06000137329102</v>
       </c>
       <c r="D3868" t="n">
-        <v>57.90000152587891</v>
+        <v>55.27999877929688</v>
       </c>
       <c r="E3868" t="n">
-        <v>57.90000152587891</v>
+        <v>55.40000152587891</v>
       </c>
       <c r="F3868" t="n">
-        <v>9659100</v>
+        <v>8452000</v>
       </c>
     </row>
     <row r="3869">
       <c r="A3869" s="1" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B3869" t="n">
-        <v>59.95999908447266</v>
+        <v>58.40999984741211</v>
       </c>
       <c r="C3869" t="n">
-        <v>59.97000122070312</v>
+        <v>59.08000183105469</v>
       </c>
       <c r="D3869" t="n">
-        <v>57.90999984741211</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="E3869" t="n">
-        <v>58.04999923706055</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="F3869" t="n">
-        <v>4338200</v>
+        <v>9659100</v>
       </c>
     </row>
     <row r="3870">
       <c r="A3870" s="1" t="n">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="B3870" t="n">
-        <v>58.5</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="C3870" t="n">
-        <v>59.54999923706055</v>
+        <v>59.97000122070312</v>
       </c>
       <c r="D3870" t="n">
-        <v>58.43999862670898</v>
+        <v>57.90999984741211</v>
       </c>
       <c r="E3870" t="n">
-        <v>58.65000152587891</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="F3870" t="n">
-        <v>7072400</v>
+        <v>4338200</v>
       </c>
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.45000076293945</v>
+        <v>58.5</v>
       </c>
       <c r="C3871" t="n">
-        <v>58.58000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3871" t="n">
-        <v>56.95000076293945</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.20000076293945</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3871" t="n">
-        <v>8390100</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B3872" t="n">
-        <v>59.20000076293945</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3872" t="n">
-        <v>59.9900016784668</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3872" t="n">
-        <v>58.20999908447266</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3872" t="n">
-        <v>59.20999908447266</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3872" t="n">
-        <v>9994900</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B3873" t="n">
-        <v>58.61000061035156</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3873" t="n">
-        <v>59.77999877929688</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3873" t="n">
-        <v>58.45999908447266</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3873" t="n">
-        <v>59.5</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3873" t="n">
-        <v>8406900</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B3874" t="n">
-        <v>57.45000076293945</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3874" t="n">
-        <v>58.93000030517578</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3874" t="n">
-        <v>57.34999847412109</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3874" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="F3874" t="n">
-        <v>5821000</v>
+        <v>8406900</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B3875" t="n">
-        <v>61.2400016784668</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="C3875" t="n">
-        <v>61.2400016784668</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3875" t="n">
-        <v>58.31999969482422</v>
+        <v>57.34999847412109</v>
       </c>
       <c r="E3875" t="n">
-        <v>58.34999847412109</v>
+        <v>58.5</v>
       </c>
       <c r="F3875" t="n">
-        <v>9826700</v>
+        <v>5821000</v>
       </c>
     </row>
     <row r="3876">
@@ -78052,19 +78052,39 @@
         <v>46253</v>
       </c>
       <c r="B3882" t="n">
-        <v>61.53</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="C3882" t="n">
-        <v>62.79</v>
+        <v>62.79000091552734</v>
       </c>
       <c r="D3882" t="n">
-        <v>61.53</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="E3882" t="n">
         <v>62</v>
       </c>
       <c r="F3882" t="n">
         <v>6589300</v>
+      </c>
+    </row>
+    <row r="3883">
+      <c r="A3883" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B3883" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="C3883" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="D3883" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E3883" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F3883" t="n">
+        <v>8006000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3883"/>
+  <dimension ref="A1:F3885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77829,262 +77829,302 @@
     </row>
     <row r="3871">
       <c r="A3871" s="1" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B3871" t="n">
-        <v>58.5</v>
+        <v>60.84999847412109</v>
       </c>
       <c r="C3871" t="n">
-        <v>59.54999923706055</v>
+        <v>61.08000183105469</v>
       </c>
       <c r="D3871" t="n">
-        <v>58.43999862670898</v>
+        <v>59.81999969482422</v>
       </c>
       <c r="E3871" t="n">
-        <v>58.65000152587891</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="F3871" t="n">
-        <v>7072400</v>
+        <v>7178400</v>
       </c>
     </row>
     <row r="3872">
       <c r="A3872" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B3872" t="n">
-        <v>58.45000076293945</v>
+        <v>58.5</v>
       </c>
       <c r="C3872" t="n">
-        <v>58.58000183105469</v>
+        <v>59.54999923706055</v>
       </c>
       <c r="D3872" t="n">
-        <v>56.95000076293945</v>
+        <v>58.43999862670898</v>
       </c>
       <c r="E3872" t="n">
-        <v>58.20000076293945</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3872" t="n">
-        <v>8390100</v>
+        <v>7072400</v>
       </c>
     </row>
     <row r="3873">
       <c r="A3873" s="1" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="B3873" t="n">
-        <v>59.20000076293945</v>
+        <v>58.45000076293945</v>
       </c>
       <c r="C3873" t="n">
-        <v>59.9900016784668</v>
+        <v>58.58000183105469</v>
       </c>
       <c r="D3873" t="n">
-        <v>58.20999908447266</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="E3873" t="n">
-        <v>59.20999908447266</v>
+        <v>58.20000076293945</v>
       </c>
       <c r="F3873" t="n">
-        <v>9994900</v>
+        <v>8390100</v>
       </c>
     </row>
     <row r="3874">
       <c r="A3874" s="1" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B3874" t="n">
-        <v>58.61000061035156</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="C3874" t="n">
-        <v>59.77999877929688</v>
+        <v>59.9900016784668</v>
       </c>
       <c r="D3874" t="n">
-        <v>58.45999908447266</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="E3874" t="n">
-        <v>59.5</v>
+        <v>59.20999908447266</v>
       </c>
       <c r="F3874" t="n">
-        <v>8406900</v>
+        <v>9994900</v>
       </c>
     </row>
     <row r="3875">
       <c r="A3875" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B3875" t="n">
-        <v>57.45000076293945</v>
+        <v>58.61000061035156</v>
       </c>
       <c r="C3875" t="n">
-        <v>58.93000030517578</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="D3875" t="n">
-        <v>57.34999847412109</v>
+        <v>58.45999908447266</v>
       </c>
       <c r="E3875" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="F3875" t="n">
-        <v>5821000</v>
+        <v>8406900</v>
       </c>
     </row>
     <row r="3876">
       <c r="A3876" s="1" t="n">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="B3876" t="n">
-        <v>59.25</v>
+        <v>57.45000076293945</v>
       </c>
       <c r="C3876" t="n">
-        <v>61.72999954223633</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3876" t="n">
-        <v>58.84999847412109</v>
+        <v>57.34999847412109</v>
       </c>
       <c r="E3876" t="n">
-        <v>61.36000061035156</v>
+        <v>58.5</v>
       </c>
       <c r="F3876" t="n">
-        <v>7752700</v>
+        <v>5821000</v>
       </c>
     </row>
     <row r="3877">
       <c r="A3877" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B3877" t="n">
-        <v>59.13999938964844</v>
+        <v>59.25</v>
       </c>
       <c r="C3877" t="n">
-        <v>59.81000137329102</v>
+        <v>61.72999954223633</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.7400016784668</v>
+        <v>58.84999847412109</v>
       </c>
       <c r="E3877" t="n">
-        <v>59.18999862670898</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="F3877" t="n">
-        <v>5522800</v>
+        <v>7752700</v>
       </c>
     </row>
     <row r="3878">
       <c r="A3878" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B3878" t="n">
-        <v>59.06999969482422</v>
+        <v>59.13999938964844</v>
       </c>
       <c r="C3878" t="n">
-        <v>59.68999862670898</v>
+        <v>59.81000137329102</v>
       </c>
       <c r="D3878" t="n">
-        <v>57.93000030517578</v>
+        <v>58.7400016784668</v>
       </c>
       <c r="E3878" t="n">
-        <v>58.4900016784668</v>
+        <v>59.18999862670898</v>
       </c>
       <c r="F3878" t="n">
-        <v>4500100</v>
+        <v>5522800</v>
       </c>
     </row>
     <row r="3879">
       <c r="A3879" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B3879" t="n">
-        <v>58.63000106811523</v>
+        <v>59.06999969482422</v>
       </c>
       <c r="C3879" t="n">
-        <v>59.38999938964844</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D3879" t="n">
-        <v>58.54999923706055</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="E3879" t="n">
-        <v>58.54999923706055</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="F3879" t="n">
-        <v>4986100</v>
+        <v>4500100</v>
       </c>
     </row>
     <row r="3880">
       <c r="A3880" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B3880" t="n">
-        <v>61.58000183105469</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="C3880" t="n">
-        <v>61.90999984741211</v>
+        <v>59.38999938964844</v>
       </c>
       <c r="D3880" t="n">
-        <v>58.70999908447266</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="E3880" t="n">
-        <v>58.70999908447266</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="F3880" t="n">
-        <v>9794400</v>
+        <v>4986100</v>
       </c>
     </row>
     <row r="3881">
       <c r="A3881" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B3881" t="n">
-        <v>61.5</v>
+        <v>61.58000183105469</v>
       </c>
       <c r="C3881" t="n">
-        <v>62.27000045776367</v>
+        <v>61.90999984741211</v>
       </c>
       <c r="D3881" t="n">
-        <v>60.97000122070312</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="E3881" t="n">
-        <v>61.79999923706055</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="F3881" t="n">
-        <v>5383200</v>
+        <v>9794400</v>
       </c>
     </row>
     <row r="3882">
       <c r="A3882" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B3882" t="n">
-        <v>61.52999877929688</v>
+        <v>61.5</v>
       </c>
       <c r="C3882" t="n">
-        <v>62.79000091552734</v>
+        <v>62.27000045776367</v>
       </c>
       <c r="D3882" t="n">
-        <v>61.52999877929688</v>
+        <v>60.97000122070312</v>
       </c>
       <c r="E3882" t="n">
-        <v>62</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="F3882" t="n">
-        <v>6589300</v>
+        <v>5383200</v>
       </c>
     </row>
     <row r="3883">
       <c r="A3883" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B3883" t="n">
+        <v>61.52999877929688</v>
+      </c>
+      <c r="C3883" t="n">
+        <v>62.79000091552734</v>
+      </c>
+      <c r="D3883" t="n">
+        <v>61.52999877929688</v>
+      </c>
+      <c r="E3883" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3883" t="n">
+        <v>6589300</v>
+      </c>
+    </row>
+    <row r="3884">
+      <c r="A3884" s="1" t="n">
         <v>46254</v>
       </c>
-      <c r="B3883" t="n">
-        <v>62.04</v>
-      </c>
-      <c r="C3883" t="n">
+      <c r="B3884" t="n">
+        <v>62.04000091552734</v>
+      </c>
+      <c r="C3884" t="n">
+        <v>62.97999954223633</v>
+      </c>
+      <c r="D3884" t="n">
+        <v>61.79999923706055</v>
+      </c>
+      <c r="E3884" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="F3884" t="n">
+        <v>8006000</v>
+      </c>
+    </row>
+    <row r="3885">
+      <c r="A3885" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B3885" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="C3885" t="n">
         <v>62.98</v>
       </c>
-      <c r="D3883" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="E3883" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="F3883" t="n">
-        <v>8006000</v>
+      <c r="D3885" t="n">
+        <v>61.82</v>
+      </c>
+      <c r="E3885" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="F3885" t="n">
+        <v>5593400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3885"/>
+  <dimension ref="A1:F3887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77949,182 +77949,222 @@
     </row>
     <row r="3877">
       <c r="A3877" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B3877" t="n">
-        <v>59.25</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="C3877" t="n">
-        <v>61.72999954223633</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.84999847412109</v>
+        <v>58.31999969482422</v>
       </c>
       <c r="E3877" t="n">
-        <v>61.36000061035156</v>
+        <v>58.34999847412109</v>
       </c>
       <c r="F3877" t="n">
-        <v>7752700</v>
+        <v>9826700</v>
       </c>
     </row>
     <row r="3878">
       <c r="A3878" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B3878" t="n">
-        <v>59.13999938964844</v>
+        <v>59.25</v>
       </c>
       <c r="C3878" t="n">
-        <v>59.81000137329102</v>
+        <v>61.72999954223633</v>
       </c>
       <c r="D3878" t="n">
-        <v>58.7400016784668</v>
+        <v>58.84999847412109</v>
       </c>
       <c r="E3878" t="n">
-        <v>59.18999862670898</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="F3878" t="n">
-        <v>5522800</v>
+        <v>7752700</v>
       </c>
     </row>
     <row r="3879">
       <c r="A3879" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B3879" t="n">
-        <v>59.06999969482422</v>
+        <v>59.13999938964844</v>
       </c>
       <c r="C3879" t="n">
-        <v>59.68999862670898</v>
+        <v>59.81000137329102</v>
       </c>
       <c r="D3879" t="n">
-        <v>57.93000030517578</v>
+        <v>58.7400016784668</v>
       </c>
       <c r="E3879" t="n">
-        <v>58.4900016784668</v>
+        <v>59.18999862670898</v>
       </c>
       <c r="F3879" t="n">
-        <v>4500100</v>
+        <v>5522800</v>
       </c>
     </row>
     <row r="3880">
       <c r="A3880" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B3880" t="n">
-        <v>58.63000106811523</v>
+        <v>59.06999969482422</v>
       </c>
       <c r="C3880" t="n">
-        <v>59.38999938964844</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D3880" t="n">
-        <v>58.54999923706055</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="E3880" t="n">
-        <v>58.54999923706055</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="F3880" t="n">
-        <v>4986100</v>
+        <v>4500100</v>
       </c>
     </row>
     <row r="3881">
       <c r="A3881" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B3881" t="n">
-        <v>61.58000183105469</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="C3881" t="n">
-        <v>61.90999984741211</v>
+        <v>59.38999938964844</v>
       </c>
       <c r="D3881" t="n">
-        <v>58.70999908447266</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="E3881" t="n">
-        <v>58.70999908447266</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="F3881" t="n">
-        <v>9794400</v>
+        <v>4986100</v>
       </c>
     </row>
     <row r="3882">
       <c r="A3882" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B3882" t="n">
-        <v>61.5</v>
+        <v>61.58000183105469</v>
       </c>
       <c r="C3882" t="n">
-        <v>62.27000045776367</v>
+        <v>61.90999984741211</v>
       </c>
       <c r="D3882" t="n">
-        <v>60.97000122070312</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="E3882" t="n">
-        <v>61.79999923706055</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="F3882" t="n">
-        <v>5383200</v>
+        <v>9794400</v>
       </c>
     </row>
     <row r="3883">
       <c r="A3883" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B3883" t="n">
-        <v>61.52999877929688</v>
+        <v>61.5</v>
       </c>
       <c r="C3883" t="n">
-        <v>62.79000091552734</v>
+        <v>62.27000045776367</v>
       </c>
       <c r="D3883" t="n">
-        <v>61.52999877929688</v>
+        <v>60.97000122070312</v>
       </c>
       <c r="E3883" t="n">
-        <v>62</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="F3883" t="n">
-        <v>6589300</v>
+        <v>5383200</v>
       </c>
     </row>
     <row r="3884">
       <c r="A3884" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B3884" t="n">
-        <v>62.04000091552734</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="C3884" t="n">
-        <v>62.97999954223633</v>
+        <v>62.79000091552734</v>
       </c>
       <c r="D3884" t="n">
-        <v>61.79999923706055</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="E3884" t="n">
-        <v>62.79999923706055</v>
+        <v>62</v>
       </c>
       <c r="F3884" t="n">
-        <v>8006000</v>
+        <v>6589300</v>
       </c>
     </row>
     <row r="3885">
       <c r="A3885" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B3885" t="n">
+        <v>62.04000091552734</v>
+      </c>
+      <c r="C3885" t="n">
+        <v>62.97999954223633</v>
+      </c>
+      <c r="D3885" t="n">
+        <v>61.79999923706055</v>
+      </c>
+      <c r="E3885" t="n">
+        <v>62.79999923706055</v>
+      </c>
+      <c r="F3885" t="n">
+        <v>8006000</v>
+      </c>
+    </row>
+    <row r="3886">
+      <c r="A3886" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B3885" t="n">
-        <v>62.85</v>
-      </c>
-      <c r="C3885" t="n">
-        <v>62.98</v>
-      </c>
-      <c r="D3885" t="n">
-        <v>61.82</v>
-      </c>
-      <c r="E3885" t="n">
-        <v>62.11</v>
-      </c>
-      <c r="F3885" t="n">
-        <v>5593400</v>
+      <c r="B3886" t="n">
+        <v>62.84999847412109</v>
+      </c>
+      <c r="C3886" t="n">
+        <v>62.97999954223633</v>
+      </c>
+      <c r="D3886" t="n">
+        <v>61.81999969482422</v>
+      </c>
+      <c r="E3886" t="n">
+        <v>62.11000061035156</v>
+      </c>
+      <c r="F3886" t="n">
+        <v>5593900</v>
+      </c>
+    </row>
+    <row r="3887">
+      <c r="A3887" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B3887" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="C3887" t="n">
+        <v>62.07</v>
+      </c>
+      <c r="D3887" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="E3887" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="F3887" t="n">
+        <v>5147800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3887"/>
+  <dimension ref="A1:F3888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78152,19 +78152,39 @@
         <v>46258</v>
       </c>
       <c r="B3887" t="n">
-        <v>61.62</v>
+        <v>61.61999893188477</v>
       </c>
       <c r="C3887" t="n">
-        <v>62.07</v>
+        <v>62.06999969482422</v>
       </c>
       <c r="D3887" t="n">
-        <v>60.7</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="E3887" t="n">
-        <v>61.92</v>
+        <v>61.91999816894531</v>
       </c>
       <c r="F3887" t="n">
         <v>5147800</v>
+      </c>
+    </row>
+    <row r="3888">
+      <c r="A3888" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B3888" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="C3888" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="D3888" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="E3888" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="F3888" t="n">
+        <v>5130900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3888"/>
+  <dimension ref="A1:F3889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78172,19 +78172,39 @@
         <v>46259</v>
       </c>
       <c r="B3888" t="n">
-        <v>60.88</v>
+        <v>60.88000106811523</v>
       </c>
       <c r="C3888" t="n">
-        <v>61.4</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="D3888" t="n">
-        <v>59.96</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="E3888" t="n">
-        <v>60.16</v>
+        <v>60.15999984741211</v>
       </c>
       <c r="F3888" t="n">
         <v>5130900</v>
+      </c>
+    </row>
+    <row r="3889">
+      <c r="A3889" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B3889" t="n">
+        <v>60.7599983215332</v>
+      </c>
+      <c r="C3889" t="n">
+        <v>61.33000183105469</v>
+      </c>
+      <c r="D3889" t="n">
+        <v>59.45999908447266</v>
+      </c>
+      <c r="E3889" t="n">
+        <v>60.04999923706055</v>
+      </c>
+      <c r="F3889" t="n">
+        <v>5961500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -77949,262 +77949,262 @@
     </row>
     <row r="3877">
       <c r="A3877" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B3877" t="n">
-        <v>61.2400016784668</v>
+        <v>59.25</v>
       </c>
       <c r="C3877" t="n">
-        <v>61.2400016784668</v>
+        <v>61.72999954223633</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.31999969482422</v>
+        <v>58.84999847412109</v>
       </c>
       <c r="E3877" t="n">
-        <v>58.34999847412109</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="F3877" t="n">
-        <v>9826700</v>
+        <v>7752700</v>
       </c>
     </row>
     <row r="3878">
       <c r="A3878" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B3878" t="n">
-        <v>59.25</v>
+        <v>59.13999938964844</v>
       </c>
       <c r="C3878" t="n">
-        <v>61.72999954223633</v>
+        <v>59.81000137329102</v>
       </c>
       <c r="D3878" t="n">
-        <v>58.84999847412109</v>
+        <v>58.7400016784668</v>
       </c>
       <c r="E3878" t="n">
-        <v>61.36000061035156</v>
+        <v>59.18999862670898</v>
       </c>
       <c r="F3878" t="n">
-        <v>7752700</v>
+        <v>5522800</v>
       </c>
     </row>
     <row r="3879">
       <c r="A3879" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B3879" t="n">
-        <v>59.13999938964844</v>
+        <v>59.06999969482422</v>
       </c>
       <c r="C3879" t="n">
-        <v>59.81000137329102</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D3879" t="n">
-        <v>58.7400016784668</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="E3879" t="n">
-        <v>59.18999862670898</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="F3879" t="n">
-        <v>5522800</v>
+        <v>4500100</v>
       </c>
     </row>
     <row r="3880">
       <c r="A3880" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B3880" t="n">
-        <v>59.06999969482422</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="C3880" t="n">
-        <v>59.68999862670898</v>
+        <v>59.38999938964844</v>
       </c>
       <c r="D3880" t="n">
-        <v>57.93000030517578</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="E3880" t="n">
-        <v>58.4900016784668</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="F3880" t="n">
-        <v>4500100</v>
+        <v>4986100</v>
       </c>
     </row>
     <row r="3881">
       <c r="A3881" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B3881" t="n">
-        <v>58.63000106811523</v>
+        <v>61.58000183105469</v>
       </c>
       <c r="C3881" t="n">
-        <v>59.38999938964844</v>
+        <v>61.90999984741211</v>
       </c>
       <c r="D3881" t="n">
-        <v>58.54999923706055</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="E3881" t="n">
-        <v>58.54999923706055</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="F3881" t="n">
-        <v>4986100</v>
+        <v>9794400</v>
       </c>
     </row>
     <row r="3882">
       <c r="A3882" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B3882" t="n">
-        <v>61.58000183105469</v>
+        <v>61.5</v>
       </c>
       <c r="C3882" t="n">
-        <v>61.90999984741211</v>
+        <v>62.27000045776367</v>
       </c>
       <c r="D3882" t="n">
-        <v>58.70999908447266</v>
+        <v>60.97000122070312</v>
       </c>
       <c r="E3882" t="n">
-        <v>58.70999908447266</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="F3882" t="n">
-        <v>9794400</v>
+        <v>5383200</v>
       </c>
     </row>
     <row r="3883">
       <c r="A3883" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B3883" t="n">
-        <v>61.5</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="C3883" t="n">
-        <v>62.27000045776367</v>
+        <v>62.79000091552734</v>
       </c>
       <c r="D3883" t="n">
-        <v>60.97000122070312</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="E3883" t="n">
-        <v>61.79999923706055</v>
+        <v>62</v>
       </c>
       <c r="F3883" t="n">
-        <v>5383200</v>
+        <v>6589300</v>
       </c>
     </row>
     <row r="3884">
       <c r="A3884" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B3884" t="n">
-        <v>61.52999877929688</v>
+        <v>62.04000091552734</v>
       </c>
       <c r="C3884" t="n">
-        <v>62.79000091552734</v>
+        <v>62.97999954223633</v>
       </c>
       <c r="D3884" t="n">
-        <v>61.52999877929688</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="E3884" t="n">
-        <v>62</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="F3884" t="n">
-        <v>6589300</v>
+        <v>8006000</v>
       </c>
     </row>
     <row r="3885">
       <c r="A3885" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B3885" t="n">
-        <v>62.04000091552734</v>
+        <v>62.84999847412109</v>
       </c>
       <c r="C3885" t="n">
         <v>62.97999954223633</v>
       </c>
       <c r="D3885" t="n">
-        <v>61.79999923706055</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="E3885" t="n">
-        <v>62.79999923706055</v>
+        <v>62.11000061035156</v>
       </c>
       <c r="F3885" t="n">
-        <v>8006000</v>
+        <v>5593900</v>
       </c>
     </row>
     <row r="3886">
       <c r="A3886" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B3886" t="n">
-        <v>62.84999847412109</v>
+        <v>61.61999893188477</v>
       </c>
       <c r="C3886" t="n">
-        <v>62.97999954223633</v>
+        <v>62.06999969482422</v>
       </c>
       <c r="D3886" t="n">
-        <v>61.81999969482422</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="E3886" t="n">
-        <v>62.11000061035156</v>
+        <v>61.91999816894531</v>
       </c>
       <c r="F3886" t="n">
-        <v>5593900</v>
+        <v>5147800</v>
       </c>
     </row>
     <row r="3887">
       <c r="A3887" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B3887" t="n">
-        <v>61.61999893188477</v>
+        <v>60.88000106811523</v>
       </c>
       <c r="C3887" t="n">
-        <v>62.06999969482422</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="D3887" t="n">
-        <v>60.70000076293945</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="E3887" t="n">
-        <v>61.91999816894531</v>
+        <v>60.15999984741211</v>
       </c>
       <c r="F3887" t="n">
-        <v>5147800</v>
+        <v>5130900</v>
       </c>
     </row>
     <row r="3888">
       <c r="A3888" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B3888" t="n">
-        <v>60.88000106811523</v>
+        <v>60.7599983215332</v>
       </c>
       <c r="C3888" t="n">
-        <v>61.40000152587891</v>
+        <v>61.33000183105469</v>
       </c>
       <c r="D3888" t="n">
-        <v>59.95999908447266</v>
+        <v>59.45999908447266</v>
       </c>
       <c r="E3888" t="n">
-        <v>60.15999984741211</v>
+        <v>60.04999923706055</v>
       </c>
       <c r="F3888" t="n">
-        <v>5130900</v>
+        <v>5966000</v>
       </c>
     </row>
     <row r="3889">
       <c r="A3889" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B3889" t="n">
-        <v>60.7599983215332</v>
+        <v>61.09</v>
       </c>
       <c r="C3889" t="n">
-        <v>61.33000183105469</v>
+        <v>61.74</v>
       </c>
       <c r="D3889" t="n">
-        <v>59.45999908447266</v>
+        <v>59.94</v>
       </c>
       <c r="E3889" t="n">
-        <v>60.04999923706055</v>
+        <v>60.76</v>
       </c>
       <c r="F3889" t="n">
-        <v>5961500</v>
+        <v>6383900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3889"/>
+  <dimension ref="A1:F3891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77949,262 +77949,302 @@
     </row>
     <row r="3877">
       <c r="A3877" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B3877" t="n">
-        <v>59.25</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="C3877" t="n">
-        <v>61.72999954223633</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="D3877" t="n">
-        <v>58.84999847412109</v>
+        <v>58.31999969482422</v>
       </c>
       <c r="E3877" t="n">
-        <v>61.36000061035156</v>
+        <v>58.34999847412109</v>
       </c>
       <c r="F3877" t="n">
-        <v>7752700</v>
+        <v>9826700</v>
       </c>
     </row>
     <row r="3878">
       <c r="A3878" s="1" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="B3878" t="n">
-        <v>59.13999938964844</v>
+        <v>59.25</v>
       </c>
       <c r="C3878" t="n">
-        <v>59.81000137329102</v>
+        <v>61.72999954223633</v>
       </c>
       <c r="D3878" t="n">
-        <v>58.7400016784668</v>
+        <v>58.84999847412109</v>
       </c>
       <c r="E3878" t="n">
-        <v>59.18999862670898</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="F3878" t="n">
-        <v>5522800</v>
+        <v>7752700</v>
       </c>
     </row>
     <row r="3879">
       <c r="A3879" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="B3879" t="n">
-        <v>59.06999969482422</v>
+        <v>59.13999938964844</v>
       </c>
       <c r="C3879" t="n">
-        <v>59.68999862670898</v>
+        <v>59.81000137329102</v>
       </c>
       <c r="D3879" t="n">
-        <v>57.93000030517578</v>
+        <v>58.7400016784668</v>
       </c>
       <c r="E3879" t="n">
-        <v>58.4900016784668</v>
+        <v>59.18999862670898</v>
       </c>
       <c r="F3879" t="n">
-        <v>4500100</v>
+        <v>5522800</v>
       </c>
     </row>
     <row r="3880">
       <c r="A3880" s="1" t="n">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="B3880" t="n">
-        <v>58.63000106811523</v>
+        <v>59.06999969482422</v>
       </c>
       <c r="C3880" t="n">
-        <v>59.38999938964844</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D3880" t="n">
-        <v>58.54999923706055</v>
+        <v>57.93000030517578</v>
       </c>
       <c r="E3880" t="n">
-        <v>58.54999923706055</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="F3880" t="n">
-        <v>4986100</v>
+        <v>4500100</v>
       </c>
     </row>
     <row r="3881">
       <c r="A3881" s="1" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B3881" t="n">
-        <v>61.58000183105469</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="C3881" t="n">
-        <v>61.90999984741211</v>
+        <v>59.38999938964844</v>
       </c>
       <c r="D3881" t="n">
-        <v>58.70999908447266</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="E3881" t="n">
-        <v>58.70999908447266</v>
+        <v>58.54999923706055</v>
       </c>
       <c r="F3881" t="n">
-        <v>9794400</v>
+        <v>4986100</v>
       </c>
     </row>
     <row r="3882">
       <c r="A3882" s="1" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B3882" t="n">
-        <v>61.5</v>
+        <v>61.58000183105469</v>
       </c>
       <c r="C3882" t="n">
-        <v>62.27000045776367</v>
+        <v>61.90999984741211</v>
       </c>
       <c r="D3882" t="n">
-        <v>60.97000122070312</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="E3882" t="n">
-        <v>61.79999923706055</v>
+        <v>58.70999908447266</v>
       </c>
       <c r="F3882" t="n">
-        <v>5383200</v>
+        <v>9794400</v>
       </c>
     </row>
     <row r="3883">
       <c r="A3883" s="1" t="n">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="B3883" t="n">
-        <v>61.52999877929688</v>
+        <v>61.5</v>
       </c>
       <c r="C3883" t="n">
-        <v>62.79000091552734</v>
+        <v>62.27000045776367</v>
       </c>
       <c r="D3883" t="n">
-        <v>61.52999877929688</v>
+        <v>60.97000122070312</v>
       </c>
       <c r="E3883" t="n">
-        <v>62</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="F3883" t="n">
-        <v>6589300</v>
+        <v>5383200</v>
       </c>
     </row>
     <row r="3884">
       <c r="A3884" s="1" t="n">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="B3884" t="n">
-        <v>62.04000091552734</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="C3884" t="n">
-        <v>62.97999954223633</v>
+        <v>62.79000091552734</v>
       </c>
       <c r="D3884" t="n">
-        <v>61.79999923706055</v>
+        <v>61.52999877929688</v>
       </c>
       <c r="E3884" t="n">
-        <v>62.79999923706055</v>
+        <v>62</v>
       </c>
       <c r="F3884" t="n">
-        <v>8006000</v>
+        <v>6589300</v>
       </c>
     </row>
     <row r="3885">
       <c r="A3885" s="1" t="n">
-        <v>46255</v>
+        <v>46254</v>
       </c>
       <c r="B3885" t="n">
-        <v>62.84999847412109</v>
+        <v>62.04000091552734</v>
       </c>
       <c r="C3885" t="n">
         <v>62.97999954223633</v>
       </c>
       <c r="D3885" t="n">
-        <v>61.81999969482422</v>
+        <v>61.79999923706055</v>
       </c>
       <c r="E3885" t="n">
-        <v>62.11000061035156</v>
+        <v>62.79999923706055</v>
       </c>
       <c r="F3885" t="n">
-        <v>5593900</v>
+        <v>8006000</v>
       </c>
     </row>
     <row r="3886">
       <c r="A3886" s="1" t="n">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B3886" t="n">
-        <v>61.61999893188477</v>
+        <v>62.84999847412109</v>
       </c>
       <c r="C3886" t="n">
-        <v>62.06999969482422</v>
+        <v>62.97999954223633</v>
       </c>
       <c r="D3886" t="n">
-        <v>60.70000076293945</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="E3886" t="n">
-        <v>61.91999816894531</v>
+        <v>62.11000061035156</v>
       </c>
       <c r="F3886" t="n">
-        <v>5147800</v>
+        <v>5593900</v>
       </c>
     </row>
     <row r="3887">
       <c r="A3887" s="1" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B3887" t="n">
-        <v>60.88000106811523</v>
+        <v>61.61999893188477</v>
       </c>
       <c r="C3887" t="n">
-        <v>61.40000152587891</v>
+        <v>62.06999969482422</v>
       </c>
       <c r="D3887" t="n">
-        <v>59.95999908447266</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="E3887" t="n">
-        <v>60.15999984741211</v>
+        <v>61.91999816894531</v>
       </c>
       <c r="F3887" t="n">
-        <v>5130900</v>
+        <v>5147800</v>
       </c>
     </row>
     <row r="3888">
       <c r="A3888" s="1" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="B3888" t="n">
-        <v>60.7599983215332</v>
+        <v>60.88000106811523</v>
       </c>
       <c r="C3888" t="n">
-        <v>61.33000183105469</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="D3888" t="n">
-        <v>59.45999908447266</v>
+        <v>59.95999908447266</v>
       </c>
       <c r="E3888" t="n">
-        <v>60.04999923706055</v>
+        <v>60.15999984741211</v>
       </c>
       <c r="F3888" t="n">
-        <v>5966000</v>
+        <v>5130900</v>
       </c>
     </row>
     <row r="3889">
       <c r="A3889" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B3889" t="n">
+        <v>60.7599983215332</v>
+      </c>
+      <c r="C3889" t="n">
+        <v>61.33000183105469</v>
+      </c>
+      <c r="D3889" t="n">
+        <v>59.45999908447266</v>
+      </c>
+      <c r="E3889" t="n">
+        <v>60.04999923706055</v>
+      </c>
+      <c r="F3889" t="n">
+        <v>5966000</v>
+      </c>
+    </row>
+    <row r="3890">
+      <c r="A3890" s="1" t="n">
         <v>46261</v>
       </c>
-      <c r="B3889" t="n">
-        <v>61.09</v>
-      </c>
-      <c r="C3889" t="n">
-        <v>61.74</v>
-      </c>
-      <c r="D3889" t="n">
-        <v>59.94</v>
-      </c>
-      <c r="E3889" t="n">
-        <v>60.76</v>
-      </c>
-      <c r="F3889" t="n">
+      <c r="B3890" t="n">
+        <v>61.09000015258789</v>
+      </c>
+      <c r="C3890" t="n">
+        <v>61.7400016784668</v>
+      </c>
+      <c r="D3890" t="n">
+        <v>59.93999862670898</v>
+      </c>
+      <c r="E3890" t="n">
+        <v>60.7599983215332</v>
+      </c>
+      <c r="F3890" t="n">
         <v>6383900</v>
+      </c>
+    </row>
+    <row r="3891">
+      <c r="A3891" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B3891" t="n">
+        <v>60.01</v>
+      </c>
+      <c r="C3891" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D3891" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="E3891" t="n">
+        <v>61</v>
+      </c>
+      <c r="F3891" t="n">
+        <v>3434400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -78232,7 +78232,7 @@
         <v>46262</v>
       </c>
       <c r="B3891" t="n">
-        <v>60.01</v>
+        <v>60.54</v>
       </c>
       <c r="C3891" t="n">
         <v>61.5</v>
@@ -78244,7 +78244,7 @@
         <v>61</v>
       </c>
       <c r="F3891" t="n">
-        <v>3434400</v>
+        <v>5010200</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -78231,18 +78231,10 @@
       <c r="A3891" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B3891" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="C3891" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="D3891" t="n">
-        <v>59.71</v>
-      </c>
-      <c r="E3891" t="n">
-        <v>61</v>
-      </c>
+      <c r="B3891" t="inlineStr"/>
+      <c r="C3891" t="inlineStr"/>
+      <c r="D3891" t="inlineStr"/>
+      <c r="E3891" t="inlineStr"/>
       <c r="F3891" t="n">
         <v>5010200</v>
       </c>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3891"/>
+  <dimension ref="A1:F3893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78231,12 +78231,60 @@
       <c r="A3891" s="1" t="n">
         <v>46262</v>
       </c>
-      <c r="B3891" t="inlineStr"/>
-      <c r="C3891" t="inlineStr"/>
-      <c r="D3891" t="inlineStr"/>
-      <c r="E3891" t="inlineStr"/>
+      <c r="B3891" t="n">
+        <v>60.54000091552734</v>
+      </c>
+      <c r="C3891" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="D3891" t="n">
+        <v>59.70999908447266</v>
+      </c>
+      <c r="E3891" t="n">
+        <v>61</v>
+      </c>
       <c r="F3891" t="n">
-        <v>5010200</v>
+        <v>5019500</v>
+      </c>
+    </row>
+    <row r="3892">
+      <c r="A3892" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B3892" t="n">
+        <v>62.68000030517578</v>
+      </c>
+      <c r="C3892" t="n">
+        <v>62.93000030517578</v>
+      </c>
+      <c r="D3892" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="E3892" t="n">
+        <v>61.79999923706055</v>
+      </c>
+      <c r="F3892" t="n">
+        <v>7090100</v>
+      </c>
+    </row>
+    <row r="3893">
+      <c r="A3893" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3893" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="C3893" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="D3893" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="E3893" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="F3893" t="n">
+        <v>7754500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3893"/>
+  <dimension ref="A1:F3894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78272,19 +78272,39 @@
         <v>46266</v>
       </c>
       <c r="B3893" t="n">
-        <v>63.99</v>
+        <v>63.9900016784668</v>
       </c>
       <c r="C3893" t="n">
-        <v>64.29000000000001</v>
+        <v>64.29000091552734</v>
       </c>
       <c r="D3893" t="n">
-        <v>62.85</v>
+        <v>62.84999847412109</v>
       </c>
       <c r="E3893" t="n">
-        <v>63.6</v>
+        <v>63.59999847412109</v>
       </c>
       <c r="F3893" t="n">
         <v>7754500</v>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B3894" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="C3894" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="D3894" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="E3894" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="F3894" t="n">
+        <v>7432300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3894"/>
+  <dimension ref="A1:F3895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78292,19 +78292,39 @@
         <v>46267</v>
       </c>
       <c r="B3894" t="n">
-        <v>64.41</v>
+        <v>64.41000366210938</v>
       </c>
       <c r="C3894" t="n">
-        <v>65.23999999999999</v>
+        <v>65.23999786376953</v>
       </c>
       <c r="D3894" t="n">
-        <v>63.13</v>
+        <v>63.13000106811523</v>
       </c>
       <c r="E3894" t="n">
-        <v>63.28</v>
+        <v>63.27999877929688</v>
       </c>
       <c r="F3894" t="n">
         <v>7432300</v>
+      </c>
+    </row>
+    <row r="3895">
+      <c r="A3895" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B3895" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="C3895" t="n">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="D3895" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="E3895" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="F3895" t="n">
+        <v>12936000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3895"/>
+  <dimension ref="A1:F3896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78315,16 +78315,36 @@
         <v>61.5</v>
       </c>
       <c r="C3895" t="n">
-        <v>64.79000000000001</v>
+        <v>64.79000091552734</v>
       </c>
       <c r="D3895" t="n">
-        <v>61.44</v>
+        <v>61.43999862670898</v>
       </c>
       <c r="E3895" t="n">
         <v>64.75</v>
       </c>
       <c r="F3895" t="n">
         <v>12936000</v>
+      </c>
+    </row>
+    <row r="3896">
+      <c r="A3896" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B3896" t="n">
+        <v>60.19</v>
+      </c>
+      <c r="C3896" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="D3896" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="E3896" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="F3896" t="n">
+        <v>8493400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -78332,16 +78332,16 @@
         <v>46269</v>
       </c>
       <c r="B3896" t="n">
-        <v>60.19</v>
+        <v>60.18999862670898</v>
       </c>
       <c r="C3896" t="n">
-        <v>61.27</v>
+        <v>61.27000045776367</v>
       </c>
       <c r="D3896" t="n">
         <v>59.5</v>
       </c>
       <c r="E3896" t="n">
-        <v>61.15</v>
+        <v>61.15000152587891</v>
       </c>
       <c r="F3896" t="n">
         <v>8493400</v>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3896"/>
+  <dimension ref="A1:F3897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78347,6 +78347,26 @@
         <v>8493400</v>
       </c>
     </row>
+    <row r="3897">
+      <c r="A3897" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B3897" t="n">
+        <v>62</v>
+      </c>
+      <c r="C3897" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="D3897" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="E3897" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="F3897" t="n">
+        <v>8111900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3897"/>
+  <dimension ref="A1:F3898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78355,16 +78355,36 @@
         <v>62</v>
       </c>
       <c r="C3897" t="n">
-        <v>63.05</v>
+        <v>63.04999923706055</v>
       </c>
       <c r="D3897" t="n">
-        <v>61.01</v>
+        <v>61.0099983215332</v>
       </c>
       <c r="E3897" t="n">
-        <v>61.04</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="F3897" t="n">
         <v>8111900</v>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B3898" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="C3898" t="n">
+        <v>63.14</v>
+      </c>
+      <c r="D3898" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="E3898" t="n">
+        <v>63</v>
+      </c>
+      <c r="F3898" t="n">
+        <v>15138900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3898"/>
+  <dimension ref="A1:F3899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78372,19 +78372,39 @@
         <v>46274</v>
       </c>
       <c r="B3898" t="n">
-        <v>62.52</v>
+        <v>62.52000045776367</v>
       </c>
       <c r="C3898" t="n">
-        <v>63.14</v>
+        <v>63.13999938964844</v>
       </c>
       <c r="D3898" t="n">
-        <v>61.85</v>
+        <v>61.84999847412109</v>
       </c>
       <c r="E3898" t="n">
         <v>63</v>
       </c>
       <c r="F3898" t="n">
         <v>15138900</v>
+      </c>
+    </row>
+    <row r="3899">
+      <c r="A3899" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B3899" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="C3899" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="D3899" t="n">
+        <v>63.05</v>
+      </c>
+      <c r="E3899" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="F3899" t="n">
+        <v>9413800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PRIO3.xlsx
+++ b/database/PRIO3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3899"/>
+  <dimension ref="A1:F3900"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78392,19 +78392,39 @@
         <v>46275</v>
       </c>
       <c r="B3899" t="n">
-        <v>64.19</v>
+        <v>64.19000244140625</v>
       </c>
       <c r="C3899" t="n">
-        <v>64.64</v>
+        <v>64.63999938964844</v>
       </c>
       <c r="D3899" t="n">
-        <v>63.05</v>
+        <v>63.04999923706055</v>
       </c>
       <c r="E3899" t="n">
-        <v>63.82</v>
+        <v>63.81999969482422</v>
       </c>
       <c r="F3899" t="n">
         <v>9413800</v>
+      </c>
+    </row>
+    <row r="3900">
+      <c r="A3900" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B3900" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="C3900" t="n">
+        <v>64.19</v>
+      </c>
+      <c r="D3900" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="E3900" t="n">
+        <v>63.47</v>
+      </c>
+      <c r="F3900" t="n">
+        <v>7334500</v>
       </c>
     </row>
   </sheetData>
